--- a/education_forms/032_educational_vr_research_participation_consent_form--education_forms.xlsx
+++ b/education_forms/032_educational_vr_research_participation_consent_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_none}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': None}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_none}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': None}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_none}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': None}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_'i_consent_for_the_participant_to_participate_in_this_vr-based_education_project'}</t>
+          <t>i_consent_for_the_participant_to_participate_in_this_vr-based_education_project</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': 'I consent for the participant to participate in this VR-based education project'}</t>
+          <t>I consent for the participant to participate in this VR-based education project</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_'i_do_not_consent_for_the_participant_to_participate_in_this_vr-based_education_project'}</t>
+          <t>i_do_not_consent_for_the_participant_to_participate_in_this_vr-based_education_project</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': 'I do not consent for the participant to participate in this VR-based education project'}</t>
+          <t>I do not consent for the participant to participate in this VR-based education project</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_none}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': None}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_none}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': None}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_none}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': None}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_none}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': None}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_none,_'label':_none}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': None, 'label': None}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
